--- a/data/trans_bre/P45C_R2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P45C_R2-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,37; -3,43</t>
+          <t>-10,52; -3,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,04; -0,03</t>
+          <t>-8,06; -0,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 2,7</t>
+          <t>-3,24; 2,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,23; 0,08</t>
+          <t>-9,69; -0,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-56,62; -23,4</t>
+          <t>-56,52; -25,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-41,58; -0,38</t>
+          <t>-40,68; -0,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-33,73; 41,2</t>
+          <t>-34,27; 37,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-37,07; 0,41</t>
+          <t>-37,78; -0,04</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,11; -1,63</t>
+          <t>-8,11; -1,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 0,09</t>
+          <t>-6,14; -0,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 2,39</t>
+          <t>-3,86; 2,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 9,97</t>
+          <t>-0,88; 9,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-43,95; -10,49</t>
+          <t>-44,54; -12,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-36,45; 0,56</t>
+          <t>-33,79; 0,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-25,16; 21,53</t>
+          <t>-26,73; 17,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 151,7</t>
+          <t>-6,21; 145,66</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 3,82</t>
+          <t>-3,82; 3,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,89; -0,08</t>
+          <t>-7,87; -0,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 6,43</t>
+          <t>-1,38; 6,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,37; -4,03</t>
+          <t>-15,48; -3,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-23,83; 31,51</t>
+          <t>-23,81; 30,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-39,31; -0,14</t>
+          <t>-39,6; -0,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 47,5</t>
+          <t>-8,91; 48,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-74,4; -24,72</t>
+          <t>-74,11; -21,75</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 1,91</t>
+          <t>-4,23; 1,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,66; -2,24</t>
+          <t>-8,61; -1,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 2,56</t>
+          <t>-4,01; 2,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,08; -1,64</t>
+          <t>-8,35; -1,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-26,51; 14,53</t>
+          <t>-24,97; 12,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-41,73; -12,76</t>
+          <t>-41,38; -9,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,45; 18,16</t>
+          <t>-22,44; 17,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-51,38; -13,9</t>
+          <t>-51,14; -14,56</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,02; -1,54</t>
+          <t>-5,02; -1,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,01; -2,46</t>
+          <t>-5,87; -2,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 1,78</t>
+          <t>-1,78; 1,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 0,41</t>
+          <t>-5,7; 0,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-30,3; -10,23</t>
+          <t>-30,18; -11,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-32,46; -14,79</t>
+          <t>-31,51; -14,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,92; 13,7</t>
+          <t>-12,48; 12,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-34,56; 1,39</t>
+          <t>-34,65; 2,31</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P45C_R2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P45C_R2-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-4,71</t>
+          <t>-4,87</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-21,71%</t>
+          <t>-22,63%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,52; -3,68</t>
+          <t>-10,37; -3,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,06; -0,08</t>
+          <t>-8,42; -0,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 2,46</t>
+          <t>-3,29; 2,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,69; -0,04</t>
+          <t>-9,62; -0,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-56,52; -25,4</t>
+          <t>-56,11; -21,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-40,68; -0,94</t>
+          <t>-41,07; -0,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-34,27; 37,39</t>
+          <t>-35,13; 40,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-37,78; -0,04</t>
+          <t>-39,23; -4,96</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,35</t>
+          <t>-0,56</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>-3,7%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,11; -1,84</t>
+          <t>-8,2; -1,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,14; -0,03</t>
+          <t>-6,23; 0,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 2,08</t>
+          <t>-4,11; 1,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 9,6</t>
+          <t>-3,71; 2,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-44,54; -12,03</t>
+          <t>-44,25; -10,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-33,79; 0,29</t>
+          <t>-35,72; 1,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-26,73; 17,63</t>
+          <t>-28,15; 15,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 145,66</t>
+          <t>-21,7; 19,59</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-8,45</t>
+          <t>-5,17</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-46,15%</t>
+          <t>-27,9%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 3,71</t>
+          <t>-4,08; 3,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,87; -0,04</t>
+          <t>-8,08; -0,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 6,77</t>
+          <t>-1,1; 6,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-15,48; -3,55</t>
+          <t>-8,88; -1,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-23,81; 30,56</t>
+          <t>-23,95; 27,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-39,6; -0,3</t>
+          <t>-38,57; -0,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 48,09</t>
+          <t>-5,89; 48,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-74,11; -21,75</t>
+          <t>-42,87; -8,28</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-4,66</t>
+          <t>-4,54</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-33,4%</t>
+          <t>-31,31%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 1,72</t>
+          <t>-3,99; 2,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,61; -1,85</t>
+          <t>-9,08; -2,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 2,55</t>
+          <t>-4,06; 2,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,35; -1,8</t>
+          <t>-7,67; -1,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,97; 12,82</t>
+          <t>-24,41; 15,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-41,38; -9,38</t>
+          <t>-43,39; -11,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,44; 17,6</t>
+          <t>-22,69; 16,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-51,14; -14,56</t>
+          <t>-46,59; -11,45</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-3,1</t>
+          <t>-3,64</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-20,11%</t>
+          <t>-21,43%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,02; -1,66</t>
+          <t>-5,0; -1,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,87; -2,35</t>
+          <t>-5,68; -2,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 1,59</t>
+          <t>-1,63; 1,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 0,54</t>
+          <t>-5,42; -1,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-30,18; -11,33</t>
+          <t>-30,11; -11,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-31,51; -14,13</t>
+          <t>-30,73; -14,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-12,48; 12,44</t>
+          <t>-11,5; 13,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-34,65; 2,31</t>
+          <t>-29,8; -11,9</t>
         </is>
       </c>
     </row>
